--- a/data/aa2_4_e.xlsx
+++ b/data/aa2_4_e.xlsx
@@ -19,9 +19,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
-  <si>
-    <t>Last produced for Price Statistics Monthly No. 4/2026, Central Bureau of Statistics</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
+  <si>
+    <t>Last produced for Price Statistics Monthly No. 7/2026, Central Bureau of Statistics</t>
   </si>
   <si>
     <t>Base: October 2017 - November 2017=414.5</t>
@@ -345,6 +345,15 @@
   </si>
   <si>
     <t>February 2026 - March 2026</t>
+  </si>
+  <si>
+    <t>March 2026 - April 2026</t>
+  </si>
+  <si>
+    <t>April 2026 - May 2026</t>
+  </si>
+  <si>
+    <t>May 2026 - June 2026</t>
   </si>
   <si>
     <t>(1)    This index serves as an indicator of changes in prices of newly-built dwellings and is not part of the Consumer Price Index framework.</t>
@@ -871,7 +880,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr defaultColWidth="4.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="28.5703125" style="8" bestFit="1" customWidth="1"/>
@@ -892,7 +901,7 @@
     </row>
     <row r="3" spans="1:5" ht="18.75">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -2578,16 +2587,16 @@
       <c r="A105" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B105" s="11">
+      <c r="B105" s="10">
         <v>536.4</v>
       </c>
-      <c r="C105" s="11">
+      <c r="C105" s="10">
         <v>0</v>
       </c>
-      <c r="D105" s="11">
+      <c r="D105" s="10">
         <v>-2.8</v>
       </c>
-      <c r="E105" s="14">
+      <c r="E105" s="13">
         <v>0.29600000000000004</v>
       </c>
     </row>
@@ -2595,69 +2604,93 @@
       <c r="A106" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B106" s="11">
-        <v>535.29999999999995</v>
-      </c>
-      <c r="C106" s="11">
-        <v>-0.2</v>
-      </c>
-      <c r="D106" s="11">
+      <c r="B106" s="10">
+        <v>534.79999999999995</v>
+      </c>
+      <c r="C106" s="10">
+        <v>-0.3</v>
+      </c>
+      <c r="D106" s="10">
         <v>-4.0999999999999996</v>
       </c>
-      <c r="E106" s="14">
-        <v>0.27300000000000002</v>
+      <c r="E106" s="13">
+        <v>0.26700000000000002</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B107" s="11">
-        <v>537.4</v>
-      </c>
-      <c r="C107" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="D107" s="11">
-        <v>-3.8</v>
-      </c>
-      <c r="E107" s="14">
+      <c r="B107" s="10">
+        <v>536.4</v>
+      </c>
+      <c r="C107" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="D107" s="10">
+        <v>-4</v>
+      </c>
+      <c r="E107" s="13">
+        <v>0.253</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B108" s="11">
+        <v>535.29999999999995</v>
+      </c>
+      <c r="C108" s="11">
+        <v>-0.2</v>
+      </c>
+      <c r="D108" s="11">
+        <v>-4.2</v>
+      </c>
+      <c r="E108" s="14">
         <v>0.28600000000000003</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="7"/>
-      <c r="B108" s="12"/>
-      <c r="C108" s="12"/>
-      <c r="D108" s="12"/>
-      <c r="E108" s="12"/>
-    </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
-      <c r="E109" s="1"/>
+      <c r="A109" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B109" s="11">
+        <v>535.29999999999995</v>
+      </c>
+      <c r="C109" s="11">
+        <v>0</v>
+      </c>
+      <c r="D109" s="11">
+        <v>-4</v>
+      </c>
+      <c r="E109" s="14">
+        <v>0.36399999999999999</v>
+      </c>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
+      <c r="A110" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B110" s="11">
+        <v>538</v>
+      </c>
+      <c r="C110" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D110" s="11">
+        <v>-2</v>
+      </c>
+      <c r="E110" s="14">
+        <v>0.38400000000000001</v>
+      </c>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
-      <c r="E111" s="1"/>
+      <c r="A111" s="7"/>
+      <c r="B111" s="12"/>
+      <c r="C111" s="12"/>
+      <c r="D111" s="12"/>
+      <c r="E111" s="12"/>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="1" t="s">
@@ -2704,19 +2737,46 @@
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
     </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A116:E116"/>
-    <mergeCell ref="A111:E111"/>
-    <mergeCell ref="A112:E112"/>
-    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A119:E119"/>
     <mergeCell ref="A114:E114"/>
     <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A118:E118"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A113:E113"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.5"/>
